--- a/data/trans_orig/Q45B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46853</t>
+          <t>45278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>47655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>685300</t>
+          <t>684589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>641498</t>
+          <t>643073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>664428</t>
+          <t>664753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1333597</t>
+          <t>1334708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1356069</t>
+          <t>1356946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>23178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65467</t>
+          <t>66441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98746</t>
+          <t>100340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77826</t>
+          <t>77649</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118130</t>
+          <t>116595</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>934333</t>
+          <t>935899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>952429</t>
+          <t>952796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>867285</t>
+          <t>865386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>901469</t>
+          <t>899907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1807130</t>
+          <t>1809159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1849230</t>
+          <t>1848318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50725</t>
+          <t>50472</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>62452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>654840</t>
+          <t>654874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>672136</t>
+          <t>671261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630688</t>
+          <t>630989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654939</t>
+          <t>654883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1293263</t>
+          <t>1293417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1321965</t>
+          <t>1321463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80857</t>
+          <t>80760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>117763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105058</t>
+          <t>107647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150185</t>
+          <t>153384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>894789</t>
+          <t>895317</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>918147</t>
+          <t>918260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>910032</t>
+          <t>912574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>950904</t>
+          <t>951617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1817107</t>
+          <t>1810100</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1862565</t>
+          <t>1860248</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72690</t>
+          <t>71108</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>222005</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>282271</t>
+          <t>284702</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>272474</t>
+          <t>274280</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>343549</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3193555</t>
+          <t>3192980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3227215</t>
+          <t>3226611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3083760</t>
+          <t>3080756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3145380</t>
+          <t>3144442</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6287720</t>
+          <t>6287354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6363238</t>
+          <t>6360052</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31300</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42698</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>683187</t>
+          <t>683552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>696530</t>
+          <t>696183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>660734</t>
+          <t>660809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>681341</t>
+          <t>680518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1348128</t>
+          <t>1350313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1373587</t>
+          <t>1374110</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>55273</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>88641</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>67365</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102516</t>
+          <t>105798</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>985894</t>
+          <t>985847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1002431</t>
+          <t>1002690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>935450</t>
+          <t>932786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>966969</t>
+          <t>967595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1927018</t>
+          <t>1925521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1967470</t>
+          <t>1965023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63173</t>
+          <t>64933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>58024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93950</t>
+          <t>94034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>716369</t>
+          <t>716309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>738348</t>
+          <t>738280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701257</t>
+          <t>699275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>730764</t>
+          <t>729360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1425031</t>
+          <t>1424642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1464136</t>
+          <t>1462742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>29541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45584</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75445</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101893</t>
+          <t>102259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145586</t>
+          <t>145138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>897249</t>
+          <t>898879</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>921108</t>
+          <t>920954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>920340</t>
+          <t>920329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>958183</t>
+          <t>960209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1829355</t>
+          <t>1828295</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1875038</t>
+          <t>1875570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>61465</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98094</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>199460</t>
+          <t>200194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>263049</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>275538</t>
+          <t>274911</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>342120</t>
+          <t>345805</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3307100</t>
+          <t>3306381</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3345692</t>
+          <t>3346047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3246987</t>
+          <t>3248968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3313750</t>
+          <t>3313699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6569184</t>
+          <t>6570313</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6643390</t>
+          <t>6646195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5776,42 +5776,42 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6530</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13138</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6530</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2782</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12492</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5889,42 +5889,42 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>15373</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9217</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24032</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15373</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9322</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24527</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>658196</t>
+          <t>657716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>669883</t>
+          <t>669868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>637411</t>
+          <t>637720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>655041</t>
+          <t>654641</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1300120</t>
+          <t>1301288</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1321967</t>
+          <t>1321874</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>45261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>53718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1001398</t>
+          <t>1001503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1012477</t>
+          <t>1012489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>990857</t>
+          <t>990446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1013836</t>
+          <t>1014422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1998069</t>
+          <t>1997897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2023217</t>
+          <t>2023961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6668,97 +6668,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4536</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5779</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4712</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>34262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744814</t>
+          <t>743750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>754279</t>
+          <t>754155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>746630</t>
+          <t>746651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>765762</t>
+          <t>766716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1497575</t>
+          <t>1497246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1517957</t>
+          <t>1517204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46845</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32672</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59258</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>915917</t>
+          <t>915796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>928422</t>
+          <t>928366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>984199</t>
+          <t>983734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1009979</t>
+          <t>1009487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1907070</t>
+          <t>1904236</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1935349</t>
+          <t>1934441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>43054</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126045</t>
+          <t>126287</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>113955</t>
+          <t>115839</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>161425</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3333318</t>
+          <t>3334937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3358024</t>
+          <t>3357023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3386030</t>
+          <t>3384644</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3427890</t>
+          <t>3426550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6728692</t>
+          <t>6729097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6778469</t>
+          <t>6776837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Habitat-trans_orig.xlsx
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47655</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>684589</t>
+          <t>683772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>643073</t>
+          <t>643865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>664753</t>
+          <t>665015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1334708</t>
+          <t>1334401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1356946</t>
+          <t>1357272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23178</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66441</t>
+          <t>65546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100340</t>
+          <t>99217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77649</t>
+          <t>78191</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116595</t>
+          <t>117913</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>935899</t>
+          <t>934175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>952796</t>
+          <t>951999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>865386</t>
+          <t>867364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>899907</t>
+          <t>901094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1809159</t>
+          <t>1807196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1848318</t>
+          <t>1847192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50472</t>
+          <t>50299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>64334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>654874</t>
+          <t>654779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>671261</t>
+          <t>671959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630989</t>
+          <t>631108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654883</t>
+          <t>654107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1293417</t>
+          <t>1292896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1321463</t>
+          <t>1322250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80760</t>
+          <t>83028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117763</t>
+          <t>121475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107647</t>
+          <t>105843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153384</t>
+          <t>152028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>895317</t>
+          <t>895957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>918260</t>
+          <t>918794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>912574</t>
+          <t>907995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>951617</t>
+          <t>948468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1810100</t>
+          <t>1815735</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1860248</t>
+          <t>1862884</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71108</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>222005</t>
+          <t>223995</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>284702</t>
+          <t>286479</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>274280</t>
+          <t>270478</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>343549</t>
+          <t>336891</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3192980</t>
+          <t>3194420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3226611</t>
+          <t>3226769</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3080756</t>
+          <t>3079454</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3144442</t>
+          <t>3144532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6287354</t>
+          <t>6294006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6360052</t>
+          <t>6363882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>30804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>683552</t>
+          <t>682227</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>696183</t>
+          <t>695937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>660809</t>
+          <t>661921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>680518</t>
+          <t>680837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1350313</t>
+          <t>1350192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1374110</t>
+          <t>1374033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55273</t>
+          <t>55720</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88641</t>
+          <t>90014</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67365</t>
+          <t>65132</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>105798</t>
+          <t>100588</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>985847</t>
+          <t>984771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1002690</t>
+          <t>1002480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>932786</t>
+          <t>932938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>967595</t>
+          <t>968041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1925521</t>
+          <t>1928719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1965023</t>
+          <t>1967220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38412</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64933</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58024</t>
+          <t>58781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94034</t>
+          <t>95269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>716309</t>
+          <t>715864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>738280</t>
+          <t>738150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699275</t>
+          <t>700510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>729360</t>
+          <t>729174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1424642</t>
+          <t>1423164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1462742</t>
+          <t>1462561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>44592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>73237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>108559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102259</t>
+          <t>100706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145138</t>
+          <t>143062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>898879</t>
+          <t>897404</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>920954</t>
+          <t>921554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>920329</t>
+          <t>922329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>960209</t>
+          <t>958916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1828295</t>
+          <t>1830721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1875570</t>
+          <t>1874714</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,82 +5083,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>32967</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>22554</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>45786</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>40183</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>55071</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>32967</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>23368</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>45214</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>40183</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>28197</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>56159</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61465</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>96528</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>200194</t>
+          <t>200743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>260980</t>
+          <t>262413</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>274911</t>
+          <t>274648</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>345805</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3306381</t>
+          <t>3307123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3346047</t>
+          <t>3343884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3248968</t>
+          <t>3249607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3313699</t>
+          <t>3312732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6570313</t>
+          <t>6570169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6646195</t>
+          <t>6644153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>657716</t>
+          <t>657157</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>669868</t>
+          <t>669992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>637720</t>
+          <t>636692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>654641</t>
+          <t>654834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1301288</t>
+          <t>1299493</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1321874</t>
+          <t>1321850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45261</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53718</t>
+          <t>53734</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1001503</t>
+          <t>1001599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1012489</t>
+          <t>1012480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>990446</t>
+          <t>989942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1014422</t>
+          <t>1014051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1997897</t>
+          <t>1998483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2023961</t>
+          <t>2023151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>34359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40270</t>
+          <t>40528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>743750</t>
+          <t>744856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>754155</t>
+          <t>754287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>746651</t>
+          <t>746740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>766716</t>
+          <t>765740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1497246</t>
+          <t>1495714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1517204</t>
+          <t>1518316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47511</t>
+          <t>47510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>59003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>915796</t>
+          <t>916190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>928366</t>
+          <t>928487</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>983734</t>
+          <t>984481</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1009487</t>
+          <t>1009870</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1904236</t>
+          <t>1906757</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1934441</t>
+          <t>1934556</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87907</t>
+          <t>86340</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126287</t>
+          <t>126815</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115839</t>
+          <t>115714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>161425</t>
+          <t>162373</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3334937</t>
+          <t>3336730</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3357023</t>
+          <t>3357336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3384644</t>
+          <t>3385728</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3426550</t>
+          <t>3426760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6729097</t>
+          <t>6729561</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6776837</t>
+          <t>6778372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
